--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486294_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486294_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.0525</v>
+        <v>11.6442</v>
       </c>
       <c r="E2" t="n">
-        <v>13.967</v>
+        <v>12.6512</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9146</v>
+        <v>-1.007</v>
       </c>
       <c r="G2" t="n">
         <v>5.2987</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0365</v>
+        <v>0.6282</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8158</v>
+        <v>0.4999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2207</v>
+        <v>0.1283</v>
       </c>
       <c r="V2" t="n">
         <v>3.7597</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2511</v>
+        <v>4.6994</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0245</v>
+        <v>4.5652</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2266</v>
+        <v>0.1341</v>
       </c>
       <c r="G3" t="n">
         <v>1.4389</v>
@@ -688,13 +688,13 @@
         <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6594</v>
+        <v>1.1077</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0721</v>
+        <v>0.6129</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5873</v>
+        <v>0.4948</v>
       </c>
       <c r="V3" t="n">
         <v>0.1952</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0088</v>
+        <v>1.874</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9276</v>
+        <v>1.0394</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0812</v>
+        <v>0.8346</v>
       </c>
       <c r="G4" t="n">
         <v>2.0038</v>
@@ -766,13 +766,13 @@
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2225</v>
+        <v>0.0877</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.3184</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1091</v>
+        <v>1.8665</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4086</v>
+        <v>2.1044</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2995</v>
+        <v>-0.2379</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7373</v>
@@ -844,13 +844,13 @@
         <v>2.6101</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6936</v>
+        <v>1.451</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0036</v>
+        <v>0.6994</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7516</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3698</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9764</v>
+        <v>0.8368</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2678</v>
+        <v>1.0634</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7086</v>
+        <v>-0.2266</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7772</v>
+        <v>-0.1681</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1915</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5857</v>
+        <v>-0.7976</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0098</v>
+        <v>1.8361</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1246</v>
+        <v>0.5324</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1147</v>
+        <v>1.3037</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7674</v>
+        <v>-2.0042</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.067</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7004</v>
+        <v>-2.1013</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6525</v>
+        <v>0.6525</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0364</v>
+        <v>0.3524</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3651</v>
+        <v>0.3149</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6713</v>
+        <v>0.0375</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1304</v>
+        <v>0.6317</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2105</v>
+        <v>0.305</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.3267</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9523</v>
@@ -1000,13 +1000,13 @@
         <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0481</v>
+        <v>-0.286</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9589</v>
+        <v>-0.4434</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0892</v>
+        <v>0.1574</v>
       </c>
       <c r="V7" t="n">
         <v>0.5649999999999999</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4215</v>
+        <v>0.3195</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1441</v>
+        <v>-0.2658</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5657</v>
+        <v>0.5853</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1681</v>
+        <v>-0.7772</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6294999999999999</v>
+        <v>-0.1915</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7976</v>
+        <v>-0.5857</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8361</v>
+        <v>-0.0098</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5324</v>
+        <v>-0.1246</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3037</v>
+        <v>0.1147</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0042</v>
+        <v>-0.7674</v>
       </c>
       <c r="N8" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.067</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1013</v>
+        <v>-0.7004</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6525</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.906</v>
+        <v>1.3795</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6044</v>
+        <v>0.8316</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3015</v>
+        <v>0.548</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MWEMA</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1918</v>
+        <v>-2.5716</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6331</v>
+        <v>-2.8214</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4413</v>
+        <v>0.2498</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1614</v>
+        <v>-1.8895</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7367</v>
+        <v>0.3314</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4247</v>
+        <v>-2.2208</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0767</v>
+        <v>-0.6391</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5229</v>
+        <v>0.2007</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5538</v>
+        <v>-0.8399</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0847</v>
+        <v>-1.2504</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2138</v>
+        <v>0.1306</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1291</v>
+        <v>-1.381</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>2.0996</v>
+        <v>0.4038</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5312</v>
+        <v>-0.0072</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5684</v>
+        <v>0.411</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.13</v>
+        <v>-0.2159</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>-0.2159</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>J. MWEMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.222</v>
+        <v>-2.7002</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2252</v>
+        <v>-2.2784</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0032</v>
+        <v>-0.4218</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8895</v>
+        <v>-2.1614</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3314</v>
+        <v>-1.7367</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2208</v>
+        <v>-0.4247</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6391</v>
+        <v>-1.0767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2007</v>
+        <v>-0.5229</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8399</v>
+        <v>-0.5538</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2504</v>
+        <v>-1.0847</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1306</v>
+        <v>-1.2138</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.381</v>
+        <v>0.1291</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.87</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2466</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.411</v>
+        <v>-0.1142</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1644</v>
+        <v>0.7054</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2159</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2159</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9458</v>
+        <v>-3.5613</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6046</v>
+        <v>-3.3126</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3412</v>
+        <v>-0.2487</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0428</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3804</v>
+        <v>-0.9959</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8904</v>
+        <v>-0.5984</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4899</v>
+        <v>-0.3975</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0575</v>
+        <v>-4.2402</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5036</v>
+        <v>-4.1178</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.1224</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4032</v>
@@ -1390,13 +1390,13 @@
         <v>2.3926</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3033</v>
+        <v>1.1206</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2007</v>
+        <v>0.5864</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1026</v>
+        <v>0.5341</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.428899999999998</v>
+        <v>8.798800000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>7.562600000000001</v>
+        <v>8.932599999999997</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1338</v>
+        <v>-0.1338999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.390399999999999</v>
+        <v>-2.3904</v>
       </c>
       <c r="H13" t="n">
         <v>-0.577700000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8126</v>
+        <v>-1.812600000000001</v>
       </c>
       <c r="J13" t="n">
         <v>14.8792</v>
@@ -1468,16 +1468,16 @@
         <v>16.313</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4702</v>
+        <v>5.840199999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7813000000000001</v>
+        <v>2.1512</v>
       </c>
       <c r="U13" t="n">
-        <v>3.689099999999999</v>
+        <v>3.689000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>3.174</v>
+        <v>3.173999999999999</v>
       </c>
       <c r="W13" t="n">
         <v>6.0403</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7855</v>
+        <v>2.5544</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5603</v>
+        <v>5.0074</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7749</v>
+        <v>-2.453</v>
       </c>
       <c r="G14" t="n">
         <v>2.6437</v>
@@ -1546,13 +1546,13 @@
         <v>0.6525</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0118</v>
+        <v>-0.2193</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8784</v>
+        <v>-0.4314</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8902</v>
+        <v>0.2121</v>
       </c>
       <c r="V14" t="n">
         <v>0.5649999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8903</v>
+        <v>2.4593</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6871</v>
+        <v>1.7988</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2033</v>
+        <v>0.6605</v>
       </c>
       <c r="G15" t="n">
         <v>5.5335</v>
@@ -1624,13 +1624,13 @@
         <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5105</v>
+        <v>-0.9415</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8099</v>
+        <v>-0.6982</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7006</v>
+        <v>-0.2434</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4319</v>
+        <v>1.97</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9631</v>
+        <v>2.0749</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5313</v>
+        <v>-0.1048</v>
       </c>
       <c r="G16" t="n">
         <v>1.6699</v>
@@ -1702,13 +1702,13 @@
         <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5431</v>
+        <v>-1.0049</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.5612</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8702</v>
+        <v>-0.4437</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0755</v>
+        <v>0.4839</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0496</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1251</v>
+        <v>1.31</v>
       </c>
       <c r="G17" t="n">
         <v>0.7537</v>
@@ -1780,13 +1780,13 @@
         <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4607</v>
+        <v>-0.0523</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3184</v>
+        <v>-0.0949</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1423</v>
+        <v>0.0427</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2855</v>
+        <v>-1.1641</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8512999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4341</v>
+        <v>-2.1142</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4226</v>
+        <v>2.1579</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9612000000000001</v>
+        <v>2.2201</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4614</v>
+        <v>-0.0622</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7865</v>
+        <v>3.8785</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1944</v>
+        <v>3.2849</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5921</v>
+        <v>0.5937</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6362</v>
+        <v>-1.7206</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7668</v>
+        <v>-1.0648</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8694</v>
+        <v>-0.6558</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6525</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4846</v>
+        <v>-0.9746</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0649</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5495</v>
+        <v>-0.2211</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2867</v>
+        <v>-1.4157</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7192</v>
+        <v>0.01</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4324</v>
+        <v>-1.4257</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4944</v>
+        <v>-1.0571</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4506</v>
+        <v>-0.1917</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0439</v>
+        <v>-0.8653999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4727</v>
+        <v>0.0467</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7022</v>
+        <v>-0.1063</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2295</v>
+        <v>0.153</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0217</v>
+        <v>-1.1038</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7484</v>
+        <v>-0.0854</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2733</v>
+        <v>-1.0184</v>
       </c>
       <c r="P19" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6422</v>
+        <v>-0.2286</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0156</v>
+        <v>-0.2319</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.0033</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3045</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.1745</v>
+        <v>0.1952</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.372</v>
+        <v>-1.613</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2335</v>
+        <v>-0.9631</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6055</v>
+        <v>-0.6499</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0571</v>
+        <v>-2.4226</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1917</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8653999999999999</v>
+        <v>-1.4614</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0467</v>
+        <v>-0.7865</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1063</v>
+        <v>-0.1944</v>
       </c>
       <c r="L20" t="n">
-        <v>0.153</v>
+        <v>-0.5921</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1038</v>
+        <v>-1.6362</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0854</v>
+        <v>-0.7668</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0184</v>
+        <v>-0.8694</v>
       </c>
       <c r="P20" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1849</v>
+        <v>0.1571</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.1766</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1765</v>
+        <v>0.3338</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4107</v>
+        <v>-1.9662</v>
       </c>
       <c r="E21" t="n">
-        <v>0.95</v>
+        <v>-2.0544</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3608</v>
+        <v>0.0883</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1579</v>
+        <v>-1.4944</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2201</v>
+        <v>-1.4506</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0622</v>
+        <v>-0.0439</v>
       </c>
       <c r="J21" t="n">
-        <v>3.8785</v>
+        <v>-0.4727</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2849</v>
+        <v>-0.7022</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5937</v>
+        <v>0.2295</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7206</v>
+        <v>-1.0217</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0648</v>
+        <v>-0.7484</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6558</v>
+        <v>-0.2733</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2212</v>
+        <v>-0.0373</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.3196</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4677</v>
+        <v>0.2824</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.695</v>
+        <v>-1.3045</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.1745</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.695</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0697</v>
+        <v>-3.6125</v>
       </c>
       <c r="E22" t="n">
         <v>-3.4353</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6344</v>
+        <v>-0.1771</v>
       </c>
       <c r="G22" t="n">
         <v>-4.7685</v>
@@ -2170,13 +2170,13 @@
         <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.1712</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2584</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3701</v>
+        <v>0.0871</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1952</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1875</v>
+        <v>-4.3802</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2048</v>
+        <v>-2.4283</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9827</v>
+        <v>-1.9519</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6256</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.06</v>
+        <v>-0.2527</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0601</v>
+        <v>-0.1634</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1201</v>
+        <v>-0.0892</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1093</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.428900000000001</v>
+        <v>-6.6841</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1337999999999995</v>
+        <v>0.1339000000000006</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.562899999999999</v>
+        <v>-6.8178</v>
       </c>
       <c r="G24" t="n">
         <v>2.3905</v>
@@ -2326,13 +2326,13 @@
         <v>14.1379</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.4703</v>
+        <v>-3.7253</v>
       </c>
       <c r="T24" t="n">
         <v>-3.6891</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7813</v>
+        <v>-0.03599999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-3.173999999999999</v>
